--- a/ViolationRecords.xlsx
+++ b/ViolationRecords.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PLPASIG\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71D86A4D-6911-433F-8761-1E6E78B36E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="155">
   <si>
     <t>NAME</t>
   </si>
@@ -467,46 +476,58 @@
   </si>
   <si>
     <t>Poncio, Clark Dave P.</t>
+  </si>
+  <si>
+    <t>1st Semester (S.Y. 2024-2025)</t>
+  </si>
+  <si>
+    <t>2nd Semester (S.Y. 2024-2025)</t>
+  </si>
+  <si>
+    <t>1st Semester (S.Y. 2025-2026)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="166" formatCode="m/d/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -514,56 +535,122 @@
         <bgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -753,22 +840,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E89"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="30.0"/>
-    <col customWidth="1" min="5" max="5" width="33.25"/>
+    <col min="1" max="1" width="25.21875" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="5" max="5" width="33.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,1452 +876,1484 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D3" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="D4" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D5" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D7" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D8" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D9" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="D10" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="D11" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="D12" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="D13" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="4">
-        <v>45456.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="D14" s="5">
+        <v>45456</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="4">
-        <v>45462.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="D15" s="5">
+        <v>45462</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="4">
-        <v>45462.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="D16" s="5">
+        <v>45462</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="4">
-        <v>45462.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="D17" s="5">
+        <v>45462</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="4">
-        <v>45470.0</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="D18" s="5">
+        <v>45470</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="4">
-        <v>45509.0</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="D19" s="5">
+        <v>45509</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="4">
-        <v>45510.0</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="D20" s="5">
+        <v>45510</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="4">
-        <v>45510.0</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="D21" s="5">
+        <v>45510</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="4">
-        <v>45531.0</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="D22" s="5">
+        <v>45531</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="E23" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
+      <c r="E24" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
+      <c r="E25" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="4">
-        <v>45580.0</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
+      <c r="D26" s="5">
+        <v>45580</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="4">
-        <v>45580.0</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
+      <c r="D27" s="5">
+        <v>45580</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="4">
-        <v>45580.0</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
+      <c r="D28" s="5">
+        <v>45580</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="6">
-        <v>45600.0</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="D29" s="7">
+        <v>45600</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="6">
-        <v>45600.0</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="D30" s="7">
+        <v>45600</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="6">
-        <v>45600.0</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="D31" s="7">
+        <v>45600</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="6">
-        <v>45600.0</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="D32" s="7">
+        <v>45600</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="6">
-        <v>45601.0</v>
-      </c>
-      <c r="E32" s="5" t="s">
+      <c r="D33" s="7">
+        <v>45601</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="6">
-        <v>45601.0</v>
-      </c>
-      <c r="E33" s="5" t="s">
+      <c r="D34" s="7">
+        <v>45601</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="6">
-        <v>45601.0</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="D35" s="7">
+        <v>45601</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D35" s="6">
-        <v>45601.0</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="D36" s="7">
+        <v>45601</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D36" s="6">
-        <v>45601.0</v>
-      </c>
-      <c r="E36" s="5" t="s">
+      <c r="D37" s="7">
+        <v>45601</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="6">
-        <v>45604.0</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
+      <c r="D38" s="7">
+        <v>45604</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="4">
-        <v>45611.0</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="s">
+      <c r="D39" s="5">
+        <v>45611</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="4">
-        <v>45622.0</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="s">
+      <c r="D40" s="5">
+        <v>45622</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="4">
-        <v>45622.0</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="s">
+      <c r="D41" s="5">
+        <v>45622</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="4">
-        <v>45622.0</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="s">
+      <c r="D42" s="5">
+        <v>45622</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C43" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="4">
-        <v>45622.0</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="s">
+      <c r="D43" s="5">
+        <v>45622</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C44" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="4">
-        <v>45622.0</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="s">
+      <c r="D44" s="5">
+        <v>45622</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D44" s="4">
-        <v>45631.0</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="s">
+      <c r="D45" s="5">
+        <v>45631</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C46" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="4">
-        <v>45643.0</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="s">
+      <c r="D46" s="5">
+        <v>45643</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="4">
-        <v>45643.0</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="s">
+      <c r="D47" s="5">
+        <v>45643</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="6">
-        <v>45664.0</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="s">
+      <c r="D48" s="7">
+        <v>45664</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B49" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D48" s="6">
-        <v>45664.0</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="s">
+      <c r="D49" s="7">
+        <v>45664</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B50" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D49" s="6">
-        <v>45666.0</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="s">
+      <c r="D50" s="7">
+        <v>45666</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="4">
-        <v>45689.0</v>
-      </c>
-      <c r="E50" s="5" t="s">
+      <c r="D51" s="5">
+        <v>45689</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B52" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D51" s="4">
-        <v>45700.0</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="s">
+      <c r="D52" s="5">
+        <v>45700</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B53" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="4">
-        <v>45714.0</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="s">
+      <c r="D53" s="5">
+        <v>45714</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B54" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="4">
-        <v>45720.0</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="s">
+      <c r="D54" s="5">
+        <v>45720</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D54" s="4">
-        <v>45721.0</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="s">
+      <c r="D55" s="5">
+        <v>45721</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B56" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D55" s="4">
-        <v>45721.0</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="s">
+      <c r="D56" s="5">
+        <v>45721</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+    </row>
+    <row r="58" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B58" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C58" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="4">
-        <v>45727.0</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="s">
+      <c r="D58" s="12">
+        <v>45727</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B59" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C59" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D57" s="4">
-        <v>45728.0</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="s">
+      <c r="D59" s="12">
+        <v>45728</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C60" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D58" s="4">
-        <v>45741.0</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="s">
+      <c r="D60" s="12">
+        <v>45741</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B61" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C61" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D59" s="4">
-        <v>45741.0</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="s">
+      <c r="D61" s="12">
+        <v>45741</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B62" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C62" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D60" s="4">
-        <v>45743.0</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="s">
+      <c r="D62" s="12">
+        <v>45743</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B63" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C63" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="4">
-        <v>45743.0</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="s">
+      <c r="D63" s="12">
+        <v>45743</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B64" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C64" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="4">
-        <v>45744.0</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="s">
+      <c r="D64" s="12">
+        <v>45744</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B65" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C65" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D63" s="4">
-        <v>45750.0</v>
-      </c>
-      <c r="E63" s="5" t="s">
+      <c r="D65" s="12">
+        <v>45750</v>
+      </c>
+      <c r="E65" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="s">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B66" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C66" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D64" s="4">
-        <v>45751.0</v>
-      </c>
-      <c r="E64" s="5" t="s">
+      <c r="D66" s="12">
+        <v>45751</v>
+      </c>
+      <c r="E66" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="s">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B67" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C67" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D65" s="4">
-        <v>45770.0</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="s">
+      <c r="D67" s="12">
+        <v>45770</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B68" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C68" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="7">
-        <v>45777.0</v>
-      </c>
-      <c r="E66" s="5" t="s">
+      <c r="D68" s="14">
+        <v>45777</v>
+      </c>
+      <c r="E68" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B69" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C69" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D67" s="4">
-        <v>45777.0</v>
-      </c>
-      <c r="E67" s="5" t="s">
+      <c r="D69" s="12">
+        <v>45777</v>
+      </c>
+      <c r="E69" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B70" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C70" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D68" s="4">
-        <v>45783.0</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="s">
+      <c r="D70" s="12">
+        <v>45783</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B71" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C71" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D69" s="4">
-        <v>45783.0</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="s">
+      <c r="D71" s="12">
+        <v>45783</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B72" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C72" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D70" s="4">
-        <v>45783.0</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="s">
+      <c r="D72" s="12">
+        <v>45783</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B73" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C73" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="4">
-        <v>45791.0</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="s">
+      <c r="D73" s="12">
+        <v>45791</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B74" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C74" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D72" s="4">
-        <v>45796.0</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="s">
+      <c r="D74" s="12">
+        <v>45796</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+    </row>
+    <row r="76" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A76" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B76" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C76" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="4">
-        <v>45903.0</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="s">
+      <c r="D76" s="19">
+        <v>45903</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B77" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C77" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D74" s="6">
-        <v>45915.0</v>
-      </c>
-      <c r="E74" s="5" t="s">
+      <c r="D77" s="21">
+        <v>45915</v>
+      </c>
+      <c r="E77" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B78" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C78" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D75" s="6">
-        <v>45930.0</v>
-      </c>
-      <c r="E75" s="5" t="s">
+      <c r="D78" s="21">
+        <v>45930</v>
+      </c>
+      <c r="E78" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B79" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C79" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D76" s="6">
-        <v>45930.0</v>
-      </c>
-      <c r="E76" s="5" t="s">
+      <c r="D79" s="21">
+        <v>45930</v>
+      </c>
+      <c r="E79" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B80" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C80" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D77" s="4">
-        <v>45937.0</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="s">
+      <c r="D80" s="19">
+        <v>45937</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B81" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C81" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="7">
-        <v>45937.0</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="s">
+      <c r="D81" s="22">
+        <v>45937</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D79" s="7">
-        <v>45953.0</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="s">
+      <c r="D82" s="22">
+        <v>45953</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B83" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C83" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D80" s="7">
-        <v>45953.0</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="s">
+      <c r="D83" s="22">
+        <v>45953</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B84" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C84" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="D81" s="4">
-        <v>45957.0</v>
-      </c>
-      <c r="E81" s="5" t="s">
+      <c r="D84" s="19">
+        <v>45957</v>
+      </c>
+      <c r="E84" s="20" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B85" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C85" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="D82" s="4">
-        <v>45958.0</v>
-      </c>
-      <c r="E82" s="5" t="s">
+      <c r="D85" s="19">
+        <v>45958</v>
+      </c>
+      <c r="E85" s="20" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B86" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C86" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D83" s="4">
-        <v>45988.0</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="s">
+      <c r="D86" s="19">
+        <v>45988</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B87" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C87" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D84" s="4">
-        <v>45988.0</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="s">
+      <c r="D87" s="19">
+        <v>45988</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B88" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C88" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D85" s="6">
-        <v>45994.0</v>
-      </c>
-      <c r="E85" s="5" t="s">
+      <c r="D88" s="21">
+        <v>45994</v>
+      </c>
+      <c r="E88" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B89" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C89" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="6">
-        <v>46052.0</v>
-      </c>
-      <c r="E86" s="5" t="s">
+      <c r="D89" s="21">
+        <v>46052</v>
+      </c>
+      <c r="E89" s="20" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A75:E75"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>